--- a/fa-tnt-ebill-import/fa-tnt-ebill-import-template.xlsx
+++ b/fa-tnt-ebill-import/fa-tnt-ebill-import-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thuy.ct\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thuan.pv\.vesper\skill-repos\itttg-Vesper-skills\fa-tnt-ebill-import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA25CDA3-F2CA-4ACC-AAE7-7B757CDF99F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{220EF392-F38A-439C-8801-416ADB597D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" activeTab="1" xr2:uid="{8F1E7E9B-2F36-49AC-9B10-FF7336557F6B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8F1E7E9B-2F36-49AC-9B10-FF7336557F6B}"/>
   </bookViews>
   <sheets>
     <sheet name="JE-Header" sheetId="1" r:id="rId1"/>
@@ -348,7 +348,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,6 +421,12 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -510,7 +516,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -544,9 +550,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -569,7 +573,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -581,7 +584,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -898,21 +905,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B136DD02-A7D0-42B8-BBB1-92B703741EB9}">
   <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.81640625" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" customWidth="1"/>
-    <col min="4" max="4" width="58.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.54296875" customWidth="1"/>
-    <col min="8" max="8" width="9.54296875" customWidth="1"/>
-    <col min="9" max="9" width="16.1796875" customWidth="1"/>
-    <col min="10" max="10" width="12.81640625" customWidth="1"/>
-    <col min="12" max="12" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" customWidth="1"/>
+    <col min="4" max="4" width="58.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="16.21875" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="10" customFormat="1" ht="76" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="10" customFormat="1" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -937,13 +944,13 @@
       <c r="J1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="43" t="s">
+      <c r="L1" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -974,11 +981,11 @@
       <c r="J2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1009,11 +1016,11 @@
       <c r="J3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -1039,17 +1046,17 @@
       <c r="J4" s="3">
         <v>7</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="31">
         <v>10324493151</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="30">
         <v>324493151</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="30">
         <v>10000000000</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -1075,17 +1082,17 @@
       <c r="J5" s="3">
         <v>7</v>
       </c>
-      <c r="L5" s="33">
+      <c r="L5" s="31">
         <v>10324493151</v>
       </c>
-      <c r="M5" s="32">
+      <c r="M5" s="30">
         <v>324493151</v>
       </c>
-      <c r="N5" s="32">
+      <c r="N5" s="30">
         <v>10000000000</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -1111,17 +1118,17 @@
       <c r="J6" s="3">
         <v>7</v>
       </c>
-      <c r="L6" s="33">
+      <c r="L6" s="31">
         <v>10324493151</v>
       </c>
-      <c r="M6" s="32">
+      <c r="M6" s="30">
         <v>324493151</v>
       </c>
-      <c r="N6" s="32">
+      <c r="N6" s="30">
         <v>10000000000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1147,13 +1154,13 @@
       <c r="J7" s="3">
         <v>7</v>
       </c>
-      <c r="L7" s="33">
+      <c r="L7" s="31">
         <v>10324493151</v>
       </c>
-      <c r="M7" s="32">
+      <c r="M7" s="30">
         <v>324493151</v>
       </c>
-      <c r="N7" s="32">
+      <c r="N7" s="30">
         <v>10000000000</v>
       </c>
     </row>
@@ -1169,45 +1176,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C1398C5-904C-49F7-9674-3AEBD223EAA3}">
   <dimension ref="A1:AG15"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.81640625" style="42" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.54296875" style="42" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.90625"/>
-    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.453125" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.1796875" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.1796875" style="16" customWidth="1"/>
-    <col min="12" max="12" width="15.90625" customWidth="1"/>
-    <col min="16" max="16" width="12.453125" customWidth="1"/>
-    <col min="17" max="19" width="8.81640625" style="24"/>
-    <col min="20" max="20" width="10.1796875" style="24" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.1796875" customWidth="1"/>
-    <col min="23" max="23" width="12.26953125" customWidth="1"/>
-    <col min="24" max="27" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" style="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.44140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.21875" style="16" customWidth="1"/>
+    <col min="12" max="12" width="15.88671875" customWidth="1"/>
+    <col min="16" max="16" width="12.44140625" customWidth="1"/>
+    <col min="17" max="19" width="8.77734375" style="23"/>
+    <col min="20" max="20" width="10.21875" style="23" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.21875" customWidth="1"/>
+    <col min="23" max="23" width="12.21875" customWidth="1"/>
+    <col min="24" max="27" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="10" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="58.54296875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="58.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="8" customFormat="1" ht="88.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" s="8" customFormat="1" ht="93" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="34" t="s">
         <v>25</v>
       </c>
       <c r="F1" s="9" t="s">
@@ -1261,26 +1267,26 @@
       <c r="AF1" s="9"/>
       <c r="AG1" s="9"/>
     </row>
-    <row r="2" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -1362,26 +1368,26 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="33" t="s">
         <v>34</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -1463,857 +1469,857 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
+    <row r="4" spans="1:33" s="44" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>0</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="28">
         <v>64281001</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="37">
         <v>100000</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="36">
+      <c r="E4" s="38"/>
+      <c r="F4" s="3">
         <v>0</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="3">
         <v>0</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="3"/>
       <c r="I4" s="3">
         <v>20260105</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="28">
         <v>64281001</v>
       </c>
       <c r="K4" s="14"/>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="3" t="s">
         <v>63</v>
       </c>
       <c r="M4" s="3">
         <v>20260105</v>
       </c>
       <c r="N4" s="3"/>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="3">
         <v>21030100</v>
       </c>
-      <c r="Q4" s="23" t="s">
+      <c r="Q4" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="R4" s="23" t="s">
+      <c r="R4" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="S4" s="23" t="s">
+      <c r="S4" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="T4" s="23" t="s">
+      <c r="T4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="U4" s="25"/>
-      <c r="V4" s="6">
+      <c r="U4" s="42"/>
+      <c r="V4" s="43">
         <v>7</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="5"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
     </row>
-    <row r="5" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" s="44" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="28">
         <v>13311001</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="38">
         <v>10000</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="36">
+      <c r="E5" s="38"/>
+      <c r="F5" s="3">
         <v>0</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="3">
         <v>0</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="3"/>
       <c r="I5" s="3">
         <v>20260105</v>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="28">
         <v>13311001</v>
       </c>
       <c r="K5" s="14"/>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="3" t="s">
         <v>63</v>
       </c>
       <c r="M5" s="3">
         <v>20260105</v>
       </c>
       <c r="N5" s="3"/>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="23"/>
-      <c r="T5" s="23"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
       <c r="U5" s="7"/>
-      <c r="V5" s="6">
+      <c r="V5" s="43">
         <v>7</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="W5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="X5" s="5">
+      <c r="X5" s="3">
         <v>100000</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Y5" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="Z5" s="25" t="s">
+      <c r="Z5" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="AA5" s="44">
+      <c r="AA5" s="45">
         <v>46032</v>
       </c>
-      <c r="AB5" s="5" t="s">
+      <c r="AB5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AC5" s="5"/>
-      <c r="AD5" s="5" t="s">
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AE5" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="AF5" s="5" t="s">
+      <c r="AF5" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AG5" s="5" t="s">
+      <c r="AG5" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" s="44" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="24">
         <v>33111001</v>
       </c>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41">
+      <c r="D6" s="38"/>
+      <c r="E6" s="38">
         <v>110000</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="3">
         <v>0</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="3">
         <v>0</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="3"/>
       <c r="I6" s="3">
         <v>20260105</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="24">
         <v>33111001</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="3" t="s">
         <v>63</v>
       </c>
       <c r="M6" s="3">
         <v>20260105</v>
       </c>
       <c r="N6" s="3"/>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="23"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
       <c r="U6" s="3"/>
-      <c r="V6" s="6">
+      <c r="V6" s="43">
         <v>7</v>
       </c>
-      <c r="W6" s="5" t="s">
+      <c r="W6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-      <c r="Z6" s="5"/>
-      <c r="AA6" s="5"/>
-      <c r="AB6" s="5"/>
-      <c r="AC6" s="5"/>
-      <c r="AD6" s="5"/>
-      <c r="AE6" s="5"/>
-      <c r="AF6" s="5"/>
-      <c r="AG6" s="5"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
     </row>
-    <row r="7" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33" s="44" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <v>0</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="28">
         <v>64281001</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="37">
         <v>100000</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="36">
+      <c r="E7" s="38"/>
+      <c r="F7" s="3">
         <v>0</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="3">
         <v>0</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="3"/>
       <c r="I7" s="3">
         <v>20260105</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="28">
         <v>64281001</v>
       </c>
       <c r="K7" s="14"/>
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="3" t="s">
         <v>64</v>
       </c>
       <c r="M7" s="3">
         <v>20260105</v>
       </c>
       <c r="N7" s="3"/>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P7" s="5">
+      <c r="P7" s="3">
         <v>21030100</v>
       </c>
-      <c r="Q7" s="23" t="s">
+      <c r="Q7" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="R7" s="23" t="s">
+      <c r="R7" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="S7" s="23" t="s">
+      <c r="S7" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="T7" s="23" t="s">
+      <c r="T7" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="U7" s="25"/>
-      <c r="V7" s="6">
+      <c r="U7" s="42"/>
+      <c r="V7" s="43">
         <v>7</v>
       </c>
-      <c r="W7" s="5" t="s">
+      <c r="W7" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="5"/>
-      <c r="AB7" s="5"/>
-      <c r="AC7" s="5"/>
-      <c r="AD7" s="5"/>
-      <c r="AE7" s="5"/>
-      <c r="AF7" s="5"/>
-      <c r="AG7" s="5"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
     </row>
-    <row r="8" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:33" s="44" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>2</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="28">
         <v>13311001</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="38">
         <v>10000</v>
       </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="36">
+      <c r="E8" s="38"/>
+      <c r="F8" s="3">
         <v>0</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="3">
         <v>0</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="3"/>
       <c r="I8" s="3">
         <v>20260105</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="28">
         <v>13311001</v>
       </c>
       <c r="K8" s="14"/>
-      <c r="L8" s="5" t="s">
+      <c r="L8" s="3" t="s">
         <v>64</v>
       </c>
       <c r="M8" s="3">
         <v>20260105</v>
       </c>
       <c r="N8" s="3"/>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="41"/>
       <c r="U8" s="7"/>
-      <c r="V8" s="6">
+      <c r="V8" s="43">
         <v>7</v>
       </c>
-      <c r="W8" s="5" t="s">
+      <c r="W8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="X8" s="5">
+      <c r="X8" s="3">
         <v>100000</v>
       </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Y8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="Z8" s="25" t="s">
+      <c r="Z8" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="AA8" s="44">
+      <c r="AA8" s="45">
         <v>46037</v>
       </c>
-      <c r="AB8" s="5" t="s">
+      <c r="AB8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AC8" s="5"/>
-      <c r="AD8" s="5" t="s">
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="AE8" s="5" t="s">
+      <c r="AE8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="AF8" s="5" t="s">
+      <c r="AF8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="AG8" s="5" t="s">
+      <c r="AG8" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" s="44" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>2</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="24">
         <v>33111001</v>
       </c>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41">
+      <c r="D9" s="38"/>
+      <c r="E9" s="38">
         <v>110000</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="3">
         <v>0</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="3"/>
       <c r="I9" s="3">
         <v>20260105</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="24">
         <v>33111001</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="L9" s="3" t="s">
         <v>64</v>
       </c>
       <c r="M9" s="3">
         <v>20260105</v>
       </c>
       <c r="N9" s="3"/>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="41"/>
+      <c r="T9" s="41"/>
       <c r="U9" s="3"/>
-      <c r="V9" s="6">
+      <c r="V9" s="43">
         <v>7</v>
       </c>
-      <c r="W9" s="5" t="s">
+      <c r="W9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5"/>
-      <c r="AB9" s="5"/>
-      <c r="AC9" s="5"/>
-      <c r="AD9" s="5"/>
-      <c r="AE9" s="5"/>
-      <c r="AF9" s="5"/>
-      <c r="AG9" s="5"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
     </row>
-    <row r="10" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:33" s="44" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>3</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="3">
         <v>0</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="28">
         <v>64281001</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="37">
         <v>100000</v>
       </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="36">
+      <c r="E10" s="38"/>
+      <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="3">
         <v>0</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="3"/>
       <c r="I10" s="3">
         <v>20260105</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10" s="28">
         <v>64281001</v>
       </c>
       <c r="K10" s="14"/>
-      <c r="L10" s="5" t="s">
+      <c r="L10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="M10" s="3">
         <v>20260105</v>
       </c>
       <c r="N10" s="3"/>
-      <c r="O10" s="5" t="s">
+      <c r="O10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P10" s="3">
         <v>21030100</v>
       </c>
-      <c r="Q10" s="23" t="s">
+      <c r="Q10" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="R10" s="23" t="s">
+      <c r="R10" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="S10" s="23" t="s">
+      <c r="S10" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="T10" s="23" t="s">
+      <c r="T10" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="U10" s="25"/>
-      <c r="V10" s="6">
+      <c r="U10" s="42"/>
+      <c r="V10" s="43">
         <v>7</v>
       </c>
-      <c r="W10" s="5" t="s">
+      <c r="W10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="5"/>
-      <c r="AD10" s="5"/>
-      <c r="AE10" s="5"/>
-      <c r="AF10" s="5"/>
-      <c r="AG10" s="5"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
     </row>
-    <row r="11" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33" s="44" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>3</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="28">
         <v>13311001</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="38">
         <v>10000</v>
       </c>
-      <c r="E11" s="41"/>
-      <c r="F11" s="36">
+      <c r="E11" s="38"/>
+      <c r="F11" s="3">
         <v>0</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="3">
         <v>0</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="3"/>
       <c r="I11" s="3">
         <v>20260105</v>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="28">
         <v>13311001</v>
       </c>
       <c r="K11" s="14"/>
-      <c r="L11" s="5" t="s">
+      <c r="L11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="M11" s="3">
         <v>20260105</v>
       </c>
       <c r="N11" s="3"/>
-      <c r="O11" s="5" t="s">
+      <c r="O11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="41"/>
+      <c r="R11" s="41"/>
+      <c r="S11" s="41"/>
+      <c r="T11" s="41"/>
       <c r="U11" s="7"/>
-      <c r="V11" s="6">
+      <c r="V11" s="43">
         <v>7</v>
       </c>
-      <c r="W11" s="5" t="s">
+      <c r="W11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="X11" s="5">
+      <c r="X11" s="3">
         <v>100000</v>
       </c>
-      <c r="Y11" s="5" t="s">
+      <c r="Y11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="Z11" s="25" t="s">
+      <c r="Z11" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="AA11" s="44">
+      <c r="AA11" s="45">
         <v>46043</v>
       </c>
-      <c r="AB11" s="5" t="s">
+      <c r="AB11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AC11" s="5"/>
-      <c r="AD11" s="5" t="s">
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="AE11" s="5" t="s">
+      <c r="AE11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="AF11" s="5" t="s">
+      <c r="AF11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AG11" s="5" t="s">
+      <c r="AG11" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:33" s="44" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>3</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="24">
         <v>33111001</v>
       </c>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41">
+      <c r="D12" s="38"/>
+      <c r="E12" s="38">
         <v>110000</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="3">
         <v>0</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="3">
         <v>0</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="3"/>
       <c r="I12" s="3">
         <v>20260105</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="24">
         <v>33111001</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="L12" s="5" t="s">
+      <c r="L12" s="3" t="s">
         <v>65</v>
       </c>
       <c r="M12" s="3">
         <v>20260105</v>
       </c>
       <c r="N12" s="3"/>
-      <c r="O12" s="5" t="s">
+      <c r="O12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="41"/>
+      <c r="T12" s="41"/>
       <c r="U12" s="3"/>
-      <c r="V12" s="6">
+      <c r="V12" s="43">
         <v>7</v>
       </c>
-      <c r="W12" s="5" t="s">
+      <c r="W12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="5"/>
-      <c r="AB12" s="5"/>
-      <c r="AC12" s="5"/>
-      <c r="AD12" s="5"/>
-      <c r="AE12" s="5"/>
-      <c r="AF12" s="5"/>
-      <c r="AG12" s="5"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
     </row>
-    <row r="13" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" s="44" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>4</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="3">
         <v>0</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="28">
         <v>64281001</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="37">
         <v>100000</v>
       </c>
-      <c r="E13" s="41"/>
-      <c r="F13" s="36">
+      <c r="E13" s="38"/>
+      <c r="F13" s="3">
         <v>0</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="3">
         <v>0</v>
       </c>
-      <c r="H13" s="5"/>
+      <c r="H13" s="3"/>
       <c r="I13" s="3">
         <v>20260105</v>
       </c>
-      <c r="J13" s="30">
+      <c r="J13" s="28">
         <v>64281001</v>
       </c>
       <c r="K13" s="14"/>
-      <c r="L13" s="5" t="s">
+      <c r="L13" s="3" t="s">
         <v>66</v>
       </c>
       <c r="M13" s="3">
         <v>20260105</v>
       </c>
       <c r="N13" s="3"/>
-      <c r="O13" s="5" t="s">
+      <c r="O13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P13" s="5">
+      <c r="P13" s="3">
         <v>21030100</v>
       </c>
-      <c r="Q13" s="23" t="s">
+      <c r="Q13" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="R13" s="23" t="s">
+      <c r="R13" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="S13" s="23" t="s">
+      <c r="S13" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="T13" s="23" t="s">
+      <c r="T13" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="U13" s="25"/>
-      <c r="V13" s="6">
+      <c r="U13" s="42"/>
+      <c r="V13" s="43">
         <v>7</v>
       </c>
-      <c r="W13" s="5" t="s">
+      <c r="W13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
-      <c r="Z13" s="5"/>
-      <c r="AA13" s="5"/>
-      <c r="AB13" s="5"/>
-      <c r="AC13" s="5"/>
-      <c r="AD13" s="5"/>
-      <c r="AE13" s="5"/>
-      <c r="AF13" s="5"/>
-      <c r="AG13" s="5"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="3"/>
     </row>
-    <row r="14" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:33" s="44" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>4</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="28">
         <v>13311001</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="38">
         <v>10000</v>
       </c>
-      <c r="E14" s="41"/>
-      <c r="F14" s="36">
+      <c r="E14" s="38"/>
+      <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="3"/>
       <c r="I14" s="3">
         <v>20260105</v>
       </c>
-      <c r="J14" s="30">
+      <c r="J14" s="28">
         <v>13311001</v>
       </c>
       <c r="K14" s="14"/>
-      <c r="L14" s="5" t="s">
+      <c r="L14" s="3" t="s">
         <v>66</v>
       </c>
       <c r="M14" s="3">
         <v>20260105</v>
       </c>
       <c r="N14" s="3"/>
-      <c r="O14" s="5" t="s">
+      <c r="O14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="41"/>
+      <c r="S14" s="41"/>
+      <c r="T14" s="41"/>
       <c r="U14" s="7"/>
-      <c r="V14" s="6">
+      <c r="V14" s="43">
         <v>7</v>
       </c>
-      <c r="W14" s="5" t="s">
+      <c r="W14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="X14" s="5">
+      <c r="X14" s="3">
         <v>100000</v>
       </c>
-      <c r="Y14" s="5" t="s">
+      <c r="Y14" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="Z14" s="25" t="s">
+      <c r="Z14" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="AA14" s="44">
+      <c r="AA14" s="45">
         <v>46053</v>
       </c>
-      <c r="AB14" s="5" t="s">
+      <c r="AB14" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="AC14" s="5"/>
-      <c r="AD14" s="5" t="s">
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="AE14" s="5" t="s">
+      <c r="AE14" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="AF14" s="5" t="s">
+      <c r="AF14" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AG14" s="5" t="s">
+      <c r="AG14" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:33" s="44" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>4</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="24">
         <v>33111001</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41">
+      <c r="D15" s="38"/>
+      <c r="E15" s="38">
         <v>110000</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="3">
         <v>0</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="3">
         <v>0</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="3"/>
       <c r="I15" s="3">
         <v>20260105</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="24">
         <v>33111001</v>
       </c>
       <c r="K15" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="L15" s="5" t="s">
+      <c r="L15" s="3" t="s">
         <v>66</v>
       </c>
       <c r="M15" s="3">
         <v>20260105</v>
       </c>
       <c r="N15" s="3"/>
-      <c r="O15" s="5" t="s">
+      <c r="O15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="41"/>
+      <c r="S15" s="41"/>
+      <c r="T15" s="41"/>
       <c r="U15" s="3"/>
-      <c r="V15" s="6">
+      <c r="V15" s="43">
         <v>7</v>
       </c>
-      <c r="W15" s="5" t="s">
+      <c r="W15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="5"/>
-      <c r="AA15" s="5"/>
-      <c r="AB15" s="5"/>
-      <c r="AC15" s="5"/>
-      <c r="AD15" s="5"/>
-      <c r="AE15" s="5"/>
-      <c r="AF15" s="5"/>
-      <c r="AG15" s="5"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:W3" xr:uid="{8C1398C5-904C-49F7-9674-3AEBD223EAA3}"/>
@@ -2322,86 +2328,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ceba343f8a154e61a69d6f3ab6653fa8 xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ceba343f8a154e61a69d6f3ab6653fa8>
-    <T_x00ec_nhTr_x1ea1_ngThanhTo_x00e1_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <Ng_x01b0__x1edd_iTr_x00ec_nh xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Ng_x01b0__x1edd_iTr_x00ec_nh>
-    <M_x1ee5_c_x0110__x00ed_chS_x1eed_d_x1ee5_ng xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <Ng_x01b0__x1edd_iThanhTo_x00e1_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Ng_x01b0__x1edd_iThanhTo_x00e1_n>
-    <Ng_x01b0__x1edd_iDuy_x1ec7_t40 xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Ng_x01b0__x1edd_iDuy_x1ec7_t40>
-    <Ng_x01b0__x1edd_iCungC_x1ea5_pTh_x00f4_ngTin xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Ng_x01b0__x1edd_iCungC_x1ea5_pTh_x00f4_ngTin>
-    <Team xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <S_x1ed1_H_x00f3_a_x0110__x01a1_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <Hi_x1ec7_uL_x1ef1_c_x0110__x1ebf_nNg_x00e0_y xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <Ng_x01b0__x1edd_iDuy_x1ec7_t xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Ng_x01b0__x1edd_iDuy_x1ec7_t>
-    <Ng_x01b0__x1edd_iDUy_x1ec7_t4 xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Ng_x01b0__x1edd_iDUy_x1ec7_t4>
-    <_Flow_SignoffStatus xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <N_x1ed9_idung xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <S_x1ed1_Ti_x1ec1_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <Ng_x01b0__x1edd_iDuy_x1ec7_t2 xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Ng_x01b0__x1edd_iDuy_x1ec7_t2>
-    <Th_x00e1_ngTr_x00ec_nhThanhTo_x00e1_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <T_x00ea_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <TaxCatchAll xmlns="184e74be-7873-4698-965f-b07e52c33735" xsi:nil="true"/>
-    <C_x00f4_ngTy xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <_x0110__x1ed1_iT_x00e1_c_x002f_NCC xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <Tags xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <DocType xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <Hi_x1ec7_uL_x1ef1_cT_x1eeb_Ng_x00e0_y xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <Th_x1edd_iH_x1ea1_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <Nofile xmlns="021df570-2223-4e8c-a451-093e8633b3bb">false</Nofile>
-    <itemFile xmlns="021df570-2223-4e8c-a451-093e8633b3bb">true</itemFile>
-    <Ph_x00e2_nlo_x1ea1_i xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-    <Uu_Tien xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2995,27 +2927,92 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ceba343f8a154e61a69d6f3ab6653fa8 xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ceba343f8a154e61a69d6f3ab6653fa8>
+    <T_x00ec_nhTr_x1ea1_ngThanhTo_x00e1_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <Ng_x01b0__x1edd_iTr_x00ec_nh xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Ng_x01b0__x1edd_iTr_x00ec_nh>
+    <M_x1ee5_c_x0110__x00ed_chS_x1eed_d_x1ee5_ng xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <Ng_x01b0__x1edd_iThanhTo_x00e1_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Ng_x01b0__x1edd_iThanhTo_x00e1_n>
+    <Ng_x01b0__x1edd_iDuy_x1ec7_t40 xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Ng_x01b0__x1edd_iDuy_x1ec7_t40>
+    <Ng_x01b0__x1edd_iCungC_x1ea5_pTh_x00f4_ngTin xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Ng_x01b0__x1edd_iCungC_x1ea5_pTh_x00f4_ngTin>
+    <Team xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <S_x1ed1_H_x00f3_a_x0110__x01a1_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <Hi_x1ec7_uL_x1ef1_c_x0110__x1ebf_nNg_x00e0_y xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <Ng_x01b0__x1edd_iDuy_x1ec7_t xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Ng_x01b0__x1edd_iDuy_x1ec7_t>
+    <Ng_x01b0__x1edd_iDUy_x1ec7_t4 xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Ng_x01b0__x1edd_iDUy_x1ec7_t4>
+    <_Flow_SignoffStatus xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <N_x1ed9_idung xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <S_x1ed1_Ti_x1ec1_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <Ng_x01b0__x1edd_iDuy_x1ec7_t2 xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Ng_x01b0__x1edd_iDuy_x1ec7_t2>
+    <Th_x00e1_ngTr_x00ec_nhThanhTo_x00e1_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="021df570-2223-4e8c-a451-093e8633b3bb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <T_x00ea_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <TaxCatchAll xmlns="184e74be-7873-4698-965f-b07e52c33735" xsi:nil="true"/>
+    <C_x00f4_ngTy xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <_x0110__x1ed1_iT_x00e1_c_x002f_NCC xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <Tags xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <DocType xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <Hi_x1ec7_uL_x1ef1_cT_x1eeb_Ng_x00e0_y xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <Th_x1edd_iH_x1ea1_n xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <Nofile xmlns="021df570-2223-4e8c-a451-093e8633b3bb">false</Nofile>
+    <itemFile xmlns="021df570-2223-4e8c-a451-093e8633b3bb">true</itemFile>
+    <Ph_x00e2_nlo_x1ea1_i xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+    <Uu_Tien xmlns="021df570-2223-4e8c-a451-093e8633b3bb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5FC039A-10D3-4E27-8A64-0E93DD51F6ED}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03548B29-A949-45C5-969C-6A63F40A3028}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="184e74be-7873-4698-965f-b07e52c33735"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="021df570-2223-4e8c-a451-093e8633b3bb"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3040,9 +3037,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03548B29-A949-45C5-969C-6A63F40A3028}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5FC039A-10D3-4E27-8A64-0E93DD51F6ED}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="184e74be-7873-4698-965f-b07e52c33735"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="021df570-2223-4e8c-a451-093e8633b3bb"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>